--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_16-07-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_16-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E49A7B-7D35-4E3B-8E75-1A440DF94FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B043E127-02AD-40E2-9752-C8B4CBD98F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31035" yWindow="1500" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33870" yWindow="1575" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="270">
   <si>
     <t>SKU</t>
   </si>
@@ -818,6 +818,18 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£39.90</t>
+  </si>
+  <si>
+    <t>£52.00</t>
+  </si>
+  <si>
+    <t>£15.52</t>
+  </si>
+  <si>
+    <t>£20.00</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1282,7 @@
         <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="J2" t="s">
         <v>138</v>
@@ -1326,7 +1338,7 @@
         <v>110</v>
       </c>
       <c r="I3" t="s">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="J3" t="s">
         <v>139</v>
@@ -1364,7 +1376,7 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>198</v>
       </c>
       <c r="D4" t="s">
         <v>68</v>
@@ -1756,13 +1768,13 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="D11" t="s">
         <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="F11" t="s">
         <v>252</v>
@@ -1812,7 +1824,7 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
         <v>76</v>
@@ -2316,7 +2328,7 @@
         <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>267</v>
       </c>
       <c r="D21" t="s">
         <v>85</v>
